--- a/assignments/a4_undergradTAC/proposal_assignments.xlsx
+++ b/assignments/a4_undergradTAC/proposal_assignments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zen/teaching/ASTR302_2026B/assignments/a4_undergradTAC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26143BD2-5E74-504D-926C-472F05EF7764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16881A85-A401-2340-9299-3D652CDF19A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46900" yWindow="-5960" windowWidth="34340" windowHeight="20500" xr2:uid="{11F34B2D-C955-3543-9CB7-DE565ED32CBD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="19480" xr2:uid="{11F34B2D-C955-3543-9CB7-DE565ED32CBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -194,9 +194,6 @@
     <t>0, 4, 11, 19</t>
   </si>
   <si>
-    <t>3, 18, 21, 27</t>
-  </si>
-  <si>
     <t>4, 17, 18, 26</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>Must Read Proposal # (If you have a number, you must read that #.pdf in the github repo, example 6 -&gt; 6.pdf)</t>
+  </si>
+  <si>
+    <t>2, 3, 5, 10, 15, 21, 25, 28</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -833,7 +833,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -841,7 +841,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -849,7 +849,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -857,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -865,7 +865,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -881,7 +881,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
